--- a/sample_data/sample_dataset_2.xlsx
+++ b/sample_data/sample_dataset_2.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Gene</t>
+          <t>Gene Symbol</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -756,11 +756,7 @@
           <t>P00003</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>GENE3</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Example protein</t>
@@ -1582,11 +1578,7 @@
           <t>P00017</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>GENE17</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>Example protein</t>
@@ -3057,11 +3049,7 @@
           <t>P00042</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>GENE42</t>
-        </is>
-      </c>
+      <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
           <t>Example protein</t>
